--- a/data/trans_camb/P8_2_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P8_2_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,27</t>
+          <t>-0,81; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,97</t>
+          <t>-0,47; 8,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,83</t>
+          <t>1,09; 10,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 7,45</t>
+          <t>-0,6; 7,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,35</t>
+          <t>-1,17; 7,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,86</t>
+          <t>5,17; 12,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,27</t>
+          <t>0,81; 6,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,77</t>
+          <t>0,02; 6,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,24</t>
+          <t>5,23; 11,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 26,3</t>
+          <t>-2,65; 25,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 27,86</t>
+          <t>-1,43; 29,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 39,03</t>
+          <t>3,42; 37,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 16,67</t>
+          <t>-1,23; 16,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 16,9</t>
+          <t>-2,47; 16,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 29,69</t>
+          <t>10,78; 29,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 16,86</t>
+          <t>1,99; 17,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 18,24</t>
+          <t>-0,05; 16,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 30,04</t>
+          <t>13,26; 30,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,06</t>
+          <t>0,36; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,32</t>
+          <t>1,03; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 40,46</t>
+          <t>5,64; 42,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,2</t>
+          <t>1,77; 6,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,39</t>
+          <t>2,9; 7,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,95</t>
+          <t>1,44; 7,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,32</t>
+          <t>1,49; 4,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,35</t>
+          <t>2,61; 5,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 23,98</t>
+          <t>4,92; 26,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 68,45</t>
+          <t>4,56; 66,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 72,33</t>
+          <t>12,79; 76,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,32; 726,91</t>
+          <t>79,83; 743,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 79,37</t>
+          <t>18,5; 78,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,36; 97,16</t>
+          <t>30,27; 96,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 87,23</t>
+          <t>16,06; 94,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,09; 61,83</t>
+          <t>17,53; 60,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,31; 75,92</t>
+          <t>31,34; 77,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,86; 342,72</t>
+          <t>62,16; 356,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,68</t>
+          <t>-2,35; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,68</t>
+          <t>-1,74; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,07</t>
+          <t>-2,34; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 1,9</t>
+          <t>-5,48; 2,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,42</t>
+          <t>-5,51; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,03</t>
+          <t>-4,68; 1,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,41</t>
+          <t>-2,64; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,65</t>
+          <t>-2,44; 2,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,8</t>
+          <t>-2,41; 2,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 97,51</t>
+          <t>-30,55; 96,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 97,93</t>
+          <t>-23,06; 99,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 64,66</t>
+          <t>-29,0; 76,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 26,38</t>
+          <t>-45,47; 27,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,51; 34,03</t>
+          <t>-45,88; 28,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 24,05</t>
+          <t>-36,69; 23,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 34,85</t>
+          <t>-28,93; 33,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 40,34</t>
+          <t>-25,56; 34,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 26,0</t>
+          <t>-25,48; 28,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,48</t>
+          <t>-0,02; 3,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,25</t>
+          <t>-1,05; 2,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 24,6</t>
+          <t>0,83; 24,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,47</t>
+          <t>0,36; 4,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,81</t>
+          <t>-2,58; 1,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,28</t>
+          <t>-6,13; 0,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,39</t>
+          <t>0,6; 3,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,46</t>
+          <t>-1,23; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 13,79</t>
+          <t>-0,94; 12,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 25,89</t>
+          <t>-0,14; 26,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 17,02</t>
+          <t>-7,02; 17,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,16; 190,09</t>
+          <t>5,79; 189,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 20,32</t>
+          <t>1,37; 20,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 8,16</t>
+          <t>-10,67; 7,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 1,27</t>
+          <t>-24,81; 0,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 18,74</t>
+          <t>2,91; 18,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 8,1</t>
+          <t>-6,36; 8,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 75,87</t>
+          <t>-4,86; 70,77</t>
         </is>
       </c>
     </row>
